--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\OneDrive - cefet-rj.br\Empresas e entrevistas\projeto logistica offshore\ofi\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\projetos\ofi\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0AE550-2B79-4406-B979-0E61E97C2145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB273FF7-7CE2-4F38-B7B3-D0A23DB7FB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$113</definedName>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="181">
   <si>
     <t>unidade</t>
   </si>
@@ -93,9 +92,6 @@
     <t>Baker Hughes Planta de Fluídos - Rio</t>
   </si>
   <si>
-    <t>BR RIO</t>
-  </si>
-  <si>
     <t>Porto de imbetiba</t>
   </si>
   <si>
@@ -571,6 +567,18 @@
   </si>
   <si>
     <t>FORSEA</t>
+  </si>
+  <si>
+    <t>BR RIO 1</t>
+  </si>
+  <si>
+    <t>BR RIO 2</t>
+  </si>
+  <si>
+    <t>BR RIO 3</t>
+  </si>
+  <si>
+    <t>fundeio</t>
   </si>
 </sst>
 </file>
@@ -639,7 +647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -652,6 +660,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -987,16 +996,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G113"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" customWidth="1"/>
+    <col min="2" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1019,7 +1029,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1036,7 +1046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1053,7 +1063,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1070,7 +1080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1087,7 +1097,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1104,7 +1114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1121,7 +1131,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1138,9 +1148,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="B9">
         <v>-22.848614000000001</v>
@@ -1149,15 +1159,15 @@
         <v>-43.146186999999998</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>180</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="B10">
         <v>-22.862100999999999</v>
@@ -1166,15 +1176,15 @@
         <v>-43.175891999999997</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>180</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="B11">
         <v>-22.838093000000001</v>
@@ -1183,15 +1193,15 @@
         <v>-43.140821000000003</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>180</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>-22.3863986649853</v>
@@ -1203,12 +1213,12 @@
         <v>11</v>
       </c>
       <c r="G12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="B13">
         <v>-21.843335</v>
@@ -1223,9 +1233,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>-22.878855000000001</v>
@@ -1240,9 +1250,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>-25.379460999999999</v>
@@ -1251,18 +1261,18 @@
         <v>-44.495949000000003</v>
       </c>
       <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
         <v>24</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>25</v>
       </c>
-      <c r="G15" t="s">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="B16">
         <v>-24.629674000000001</v>
@@ -1271,18 +1281,18 @@
         <v>-42.264716999999997</v>
       </c>
       <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" t="s">
         <v>28</v>
       </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="B17">
         <v>-21.943075</v>
@@ -1291,18 +1301,18 @@
         <v>-39.759360999999998</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="B18">
         <f>-24.558464</f>
@@ -1312,15 +1322,15 @@
         <v>-42.187762999999997</v>
       </c>
       <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" t="s">
         <v>28</v>
       </c>
-      <c r="G18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>-23.253872999999999</v>
@@ -1329,15 +1339,15 @@
         <v>-39.568072999999998</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>-23.513114999999999</v>
@@ -1346,21 +1356,21 @@
         <v>-41.064297000000003</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
         <v>35</v>
       </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" t="s">
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="B21">
         <v>-21.938911000000001</v>
@@ -1369,21 +1379,21 @@
         <v>-39.784574999999997</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="B22">
         <v>-21.214009999999998</v>
@@ -1392,18 +1402,18 @@
         <v>-39.997269000000003</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23">
         <v>-21.33</v>
@@ -1412,12 +1422,12 @@
         <v>-40.07</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24">
         <v>-23.516300000000001</v>
@@ -1426,21 +1436,21 @@
         <v>-41.061</v>
       </c>
       <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>42</v>
-      </c>
-      <c r="E24" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>43</v>
       </c>
       <c r="B25">
         <v>-19.86</v>
@@ -1449,18 +1459,18 @@
         <v>-39.619999999999997</v>
       </c>
       <c r="D25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" t="s">
         <v>44</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>45</v>
-      </c>
-      <c r="F25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>46</v>
       </c>
       <c r="B26">
         <v>-22.87</v>
@@ -1469,15 +1479,15 @@
         <v>-43.13</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B27">
         <v>-21.26</v>
@@ -1486,40 +1496,40 @@
         <v>-40.01</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" t="s">
         <v>48</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>49</v>
       </c>
-      <c r="F28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="D29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>50</v>
-      </c>
-      <c r="D29" t="s">
-        <v>49</v>
-      </c>
-      <c r="F29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>51</v>
       </c>
       <c r="B30">
         <v>-21.251000000000001</v>
@@ -1528,18 +1538,18 @@
         <v>-40.002000000000002</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31">
         <v>-21.1599</v>
@@ -1548,29 +1558,29 @@
         <v>-39.978400000000001</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G31" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>53</v>
-      </c>
-      <c r="D32" t="s">
-        <v>49</v>
-      </c>
-      <c r="F32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>54</v>
       </c>
       <c r="B33">
         <v>-22.6</v>
@@ -1579,15 +1589,15 @@
         <v>-40.26</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B34">
         <v>-22.39</v>
@@ -1596,18 +1606,18 @@
         <v>-40.1</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>56</v>
-      </c>
-      <c r="F34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>57</v>
       </c>
       <c r="B35">
         <v>-22.46</v>
@@ -1616,18 +1626,18 @@
         <v>-40.049999999999997</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>58</v>
-      </c>
-      <c r="F35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>59</v>
       </c>
       <c r="B36">
         <v>-23.133800000000001</v>
@@ -1636,21 +1646,21 @@
         <v>-41.071300000000001</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" t="s">
         <v>60</v>
       </c>
-      <c r="F36" t="s">
-        <v>31</v>
-      </c>
-      <c r="G36" t="s">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>62</v>
       </c>
       <c r="B37">
         <v>-22.95</v>
@@ -1659,21 +1669,21 @@
         <v>-40.72</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B38">
         <v>54.109959000000003</v>
@@ -1682,18 +1692,18 @@
         <v>7.4783869999999997</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G38" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B39">
         <v>-25.139942000000001</v>
@@ -1702,21 +1712,21 @@
         <v>-42.944110999999999</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
+        <v>102</v>
+      </c>
+      <c r="G39" t="s">
         <v>103</v>
       </c>
-      <c r="G39" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B40">
         <v>-25.393484000000001</v>
@@ -1725,18 +1735,18 @@
         <v>-42.761291999999997</v>
       </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F40" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" t="s">
         <v>103</v>
       </c>
-      <c r="G40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B41">
         <v>-25.202905999999999</v>
@@ -1745,18 +1755,18 @@
         <v>-42.878483000000003</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F41" t="s">
+        <v>102</v>
+      </c>
+      <c r="G41" t="s">
         <v>103</v>
       </c>
-      <c r="G41" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B42">
         <v>-25.447762999999998</v>
@@ -1765,18 +1775,18 @@
         <v>-42.752960000000002</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F42" t="s">
+        <v>102</v>
+      </c>
+      <c r="G42" t="s">
         <v>103</v>
       </c>
-      <c r="G42" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B43">
         <v>-25.490202</v>
@@ -1785,18 +1795,18 @@
         <v>-42.781055000000002</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
+        <v>102</v>
+      </c>
+      <c r="G43" t="s">
         <v>103</v>
       </c>
-      <c r="G43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B44">
         <v>-25.517744</v>
@@ -1805,18 +1815,18 @@
         <v>-43.466293</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G44" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45">
         <v>-22.0852</v>
@@ -1825,18 +1835,18 @@
         <v>-39.827500000000001</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B46">
         <v>-21.882000000000001</v>
@@ -1845,21 +1855,21 @@
         <v>-39.8598</v>
       </c>
       <c r="D46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G46" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>67</v>
       </c>
       <c r="B47">
         <v>-22.22</v>
@@ -1868,18 +1878,18 @@
         <v>-40.33</v>
       </c>
       <c r="D47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B48">
         <v>-23.317</v>
@@ -1888,21 +1898,21 @@
         <v>-41.255200000000002</v>
       </c>
       <c r="D48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G48" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>70</v>
       </c>
       <c r="B49">
         <v>-22.16</v>
@@ -1911,29 +1921,29 @@
         <v>-40.14</v>
       </c>
       <c r="D49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>71</v>
-      </c>
-      <c r="D50" t="s">
-        <v>49</v>
-      </c>
-      <c r="F50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>72</v>
       </c>
       <c r="B51">
         <v>-21.33</v>
@@ -1942,29 +1952,29 @@
         <v>-40.01</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G51" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>72</v>
+      </c>
+      <c r="D52" t="s">
+        <v>43</v>
+      </c>
+      <c r="F52" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>73</v>
-      </c>
-      <c r="D52" t="s">
-        <v>44</v>
-      </c>
-      <c r="F52" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>74</v>
       </c>
       <c r="B53">
         <v>-21.975999999999999</v>
@@ -1973,18 +1983,18 @@
         <v>-39.725000000000001</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B54">
         <v>-23.5244</v>
@@ -1993,32 +2003,32 @@
         <v>-41.081299999999999</v>
       </c>
       <c r="D54" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" t="s">
         <v>44</v>
       </c>
-      <c r="E54" t="s">
-        <v>45</v>
-      </c>
       <c r="F54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>76</v>
-      </c>
-      <c r="D55" t="s">
-        <v>44</v>
-      </c>
-      <c r="F55" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>77</v>
       </c>
       <c r="B56">
         <v>-21.942143999999999</v>
@@ -2027,18 +2037,18 @@
         <v>-39.726315</v>
       </c>
       <c r="D56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E56" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B57">
         <v>-21.245633999999999</v>
@@ -2047,21 +2057,21 @@
         <v>-40.031886999999998</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F57" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G57" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B58">
         <v>-25.246302</v>
@@ -2070,21 +2080,21 @@
         <v>-42.538494</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G58" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B59">
         <v>-22.37</v>
@@ -2093,18 +2103,18 @@
         <v>-40.04</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F59" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B60">
         <v>5.2855800000000004</v>
@@ -2113,54 +2123,54 @@
         <v>-50.104092000000001</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F60" t="s">
+        <v>172</v>
+      </c>
+      <c r="G60" t="s">
         <v>173</v>
       </c>
-      <c r="G60" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>80</v>
       </c>
-      <c r="D61" t="s">
-        <v>49</v>
-      </c>
-      <c r="F61" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="D62" t="s">
+        <v>48</v>
+      </c>
+      <c r="F62" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>81</v>
       </c>
-      <c r="D62" t="s">
-        <v>49</v>
-      </c>
-      <c r="F62" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="D63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F63" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>82</v>
-      </c>
-      <c r="D63" t="s">
-        <v>49</v>
-      </c>
-      <c r="F63" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>83</v>
       </c>
       <c r="B64">
         <v>-23.39</v>
@@ -2169,29 +2179,29 @@
         <v>-41.4</v>
       </c>
       <c r="D64" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65" t="s">
+        <v>48</v>
+      </c>
+      <c r="F65" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>84</v>
-      </c>
-      <c r="D65" t="s">
-        <v>49</v>
-      </c>
-      <c r="F65" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>85</v>
       </c>
       <c r="B66">
         <v>-22.96</v>
@@ -2200,18 +2210,18 @@
         <v>-40.72</v>
       </c>
       <c r="D66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B67">
         <v>-22.672789000000002</v>
@@ -2220,18 +2230,18 @@
         <v>-40.546345000000002</v>
       </c>
       <c r="D67" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B68">
         <v>-22.13</v>
@@ -2240,37 +2250,52 @@
         <v>-39.96</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B69">
+        <v>-22.561312000000001</v>
+      </c>
+      <c r="C69">
+        <v>-40.122622999999997</v>
+      </c>
+      <c r="D69" t="s">
+        <v>78</v>
+      </c>
+      <c r="F69" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>87</v>
       </c>
-      <c r="D69" t="s">
-        <v>79</v>
-      </c>
-      <c r="F69" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B70" s="6">
+        <v>-22.546870999999999</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-40.067348000000003</v>
+      </c>
+      <c r="D70" t="s">
+        <v>78</v>
+      </c>
+      <c r="F70" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>88</v>
-      </c>
-      <c r="F70" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>89</v>
       </c>
       <c r="B71">
         <v>-22.55</v>
@@ -2279,18 +2304,18 @@
         <v>-40.25</v>
       </c>
       <c r="D71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B72">
         <v>-22.34</v>
@@ -2299,18 +2324,18 @@
         <v>-40.19</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B73">
         <v>-22.66</v>
@@ -2319,40 +2344,52 @@
         <v>-40.229999999999997</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G73" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B74">
+        <v>-22.633976000000001</v>
+      </c>
+      <c r="C74">
+        <v>-40.093547999999998</v>
+      </c>
+      <c r="D74" t="s">
+        <v>78</v>
+      </c>
+      <c r="F74" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>93</v>
       </c>
-      <c r="D74" t="s">
-        <v>79</v>
-      </c>
-      <c r="F74" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="B75">
+        <v>-21.906445000000001</v>
+      </c>
+      <c r="C75">
+        <v>-39.735923999999997</v>
+      </c>
+      <c r="D75" t="s">
+        <v>78</v>
+      </c>
+      <c r="F75" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>94</v>
-      </c>
-      <c r="D75" t="s">
-        <v>79</v>
-      </c>
-      <c r="F75" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>95</v>
       </c>
       <c r="B76">
         <v>-22.42</v>
@@ -2361,15 +2398,15 @@
         <v>-39.950000000000003</v>
       </c>
       <c r="D76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F76" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B77">
         <v>-21.96</v>
@@ -2378,18 +2415,18 @@
         <v>-39.82</v>
       </c>
       <c r="D77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G77" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B78">
         <v>-21.99</v>
@@ -2398,15 +2435,15 @@
         <v>-39.729999999999997</v>
       </c>
       <c r="D78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F78" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B79">
         <v>-22.62</v>
@@ -2415,18 +2452,18 @@
         <v>-39.979999999999997</v>
       </c>
       <c r="D79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G79" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="B80">
         <v>-21.23</v>
@@ -2435,18 +2472,18 @@
         <v>-40.04</v>
       </c>
       <c r="D80" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F80" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G80" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B81">
         <v>-22.701767</v>
@@ -2455,18 +2492,18 @@
         <v>-40.677059</v>
       </c>
       <c r="D81" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B82">
         <v>-25.601856000000002</v>
@@ -2475,18 +2512,18 @@
         <v>-42.820484</v>
       </c>
       <c r="D82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F82" t="s">
+        <v>102</v>
+      </c>
+      <c r="G82" t="s">
         <v>103</v>
       </c>
-      <c r="G82" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B83">
         <v>-25.328738999999999</v>
@@ -2495,18 +2532,18 @@
         <v>-42.692242</v>
       </c>
       <c r="D83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F83" t="s">
+        <v>102</v>
+      </c>
+      <c r="G83" t="s">
         <v>103</v>
       </c>
-      <c r="G83" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B84">
         <v>-25.022000999999999</v>
@@ -2515,18 +2552,18 @@
         <v>-42.667259000000001</v>
       </c>
       <c r="D84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G84" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B85">
         <v>-25.656942000000001</v>
@@ -2535,18 +2572,18 @@
         <v>-42.858749000000003</v>
       </c>
       <c r="D85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F85" t="s">
+        <v>102</v>
+      </c>
+      <c r="G85" t="s">
         <v>103</v>
       </c>
-      <c r="G85" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B86">
         <v>-24.951167999999999</v>
@@ -2555,18 +2592,18 @@
         <v>-42.467758000000003</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G86" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B87">
         <v>-24.776168999999999</v>
@@ -2575,18 +2612,18 @@
         <v>-42.720005</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F87" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G87" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B88">
         <v>-24.64</v>
@@ -2595,18 +2632,18 @@
         <v>-42.51</v>
       </c>
       <c r="D88" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G88" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B89">
         <v>37.594048000000001</v>
@@ -2615,18 +2652,18 @@
         <v>121.40307</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F89" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G89" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B90">
         <v>-24.78</v>
@@ -2635,18 +2672,18 @@
         <v>-42.5</v>
       </c>
       <c r="D90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G90" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B91">
         <v>-24.68</v>
@@ -2655,18 +2692,18 @@
         <v>-42.5</v>
       </c>
       <c r="D91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F91" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G91" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B92">
         <v>-24.63</v>
@@ -2675,18 +2712,18 @@
         <v>-42.41</v>
       </c>
       <c r="D92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G92" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B93">
         <v>-24.67</v>
@@ -2695,18 +2732,18 @@
         <v>-42.38</v>
       </c>
       <c r="D93" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F93" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G93" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B94">
         <v>-24.54</v>
@@ -2715,18 +2752,18 @@
         <v>-42.46</v>
       </c>
       <c r="D94" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F94" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G94" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="B95">
         <v>-24.59</v>
@@ -2735,18 +2772,18 @@
         <v>-42.56</v>
       </c>
       <c r="D95" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F95" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G95" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B96">
         <v>-24.74</v>
@@ -2755,18 +2792,18 @@
         <v>-42.51</v>
       </c>
       <c r="D96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G96" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B97">
         <v>-25.798373999999999</v>
@@ -2775,18 +2812,18 @@
         <v>-43.262680000000003</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F97" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G97" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="B98">
         <v>-25.671883000000001</v>
@@ -2795,18 +2832,18 @@
         <v>-43.205939999999998</v>
       </c>
       <c r="D98" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G98" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B99">
         <v>-25.226118</v>
@@ -2815,18 +2852,18 @@
         <v>-42.56982</v>
       </c>
       <c r="D99" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G99" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B100">
         <v>-24.685623</v>
@@ -2835,18 +2872,18 @@
         <v>-42.293922000000002</v>
       </c>
       <c r="D100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G100" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="B101">
         <v>-22.1</v>
@@ -2855,15 +2892,15 @@
         <v>-39.909999999999997</v>
       </c>
       <c r="D101" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F101" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B102">
         <v>-23.08</v>
@@ -2872,37 +2909,46 @@
         <v>-40.99</v>
       </c>
       <c r="D102" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G102" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
+      <c r="D103" t="s">
         <v>117</v>
       </c>
-      <c r="D103" t="s">
+      <c r="F103" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F103" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
+      <c r="B104">
+        <v>4.5487399999999996</v>
+      </c>
+      <c r="C104">
+        <v>4.5609250000000001</v>
+      </c>
+      <c r="D104" t="s">
+        <v>78</v>
+      </c>
+      <c r="F104" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="F104" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="B105">
         <v>-22.14</v>
@@ -2911,15 +2957,15 @@
         <v>-39.92</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F105" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B106">
         <v>-22.14</v>
@@ -2928,15 +2974,15 @@
         <v>-39.92</v>
       </c>
       <c r="D106" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F106" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B107">
         <v>-23.3827</v>
@@ -2945,48 +2991,60 @@
         <v>-40.073999999999998</v>
       </c>
       <c r="D107" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E107" t="s">
+        <v>122</v>
+      </c>
+      <c r="F107" t="s">
+        <v>102</v>
+      </c>
+      <c r="G107" t="s">
         <v>123</v>
       </c>
-      <c r="F107" t="s">
-        <v>103</v>
-      </c>
-      <c r="G107" t="s">
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
+      <c r="B108">
+        <v>-22.657520000000002</v>
+      </c>
+      <c r="C108">
+        <v>-40.140785000000001</v>
+      </c>
+      <c r="D108" t="s">
+        <v>23</v>
+      </c>
+      <c r="F108" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D108" t="s">
-        <v>24</v>
-      </c>
-      <c r="F108" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
+      <c r="D109" t="s">
+        <v>48</v>
+      </c>
+      <c r="F109" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F109" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
+      <c r="D110" t="s">
+        <v>48</v>
+      </c>
+      <c r="F110" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>127</v>
-      </c>
-      <c r="F110" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>128</v>
       </c>
       <c r="B111">
         <v>-21.33</v>
@@ -2995,21 +3053,21 @@
         <v>-40.049999999999997</v>
       </c>
       <c r="D111" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E111" t="s">
+        <v>128</v>
+      </c>
+      <c r="F111" t="s">
         <v>129</v>
       </c>
-      <c r="F111" t="s">
-        <v>130</v>
-      </c>
       <c r="G111" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B112">
         <v>-22.436900000000001</v>
@@ -3018,18 +3076,18 @@
         <v>-40.425800000000002</v>
       </c>
       <c r="D112" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G112" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="5" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="B113">
         <v>-22.374779</v>
@@ -3038,29 +3096,17 @@
         <v>-40.417454999999997</v>
       </c>
       <c r="D113" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F113" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G113" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G113" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A458B0-5351-487A-ABCF-BB5088AD3353}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\projetos\ofi\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB273FF7-7CE2-4F38-B7B3-D0A23DB7FB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C9BC0C-60C9-436F-9E67-AACC10C0FCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$114</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="181">
   <si>
     <t>unidade</t>
   </si>
@@ -545,9 +545,6 @@
     <t>PETROBRAS 84 (P-84)</t>
   </si>
   <si>
-    <t>na</t>
-  </si>
-  <si>
     <t>NORBE IX</t>
   </si>
   <si>
@@ -579,6 +576,9 @@
   </si>
   <si>
     <t>fundeio</t>
+  </si>
+  <si>
+    <t>PETROBRAS 82 (P-82)</t>
   </si>
 </sst>
 </file>
@@ -995,7 +995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.88671875" customWidth="1"/>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B9">
         <v>-22.848614000000001</v>
@@ -1159,7 +1159,7 @@
         <v>-43.146186999999998</v>
       </c>
       <c r="D9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" t="s">
         <v>135</v>
@@ -1167,7 +1167,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B10">
         <v>-22.862100999999999</v>
@@ -1176,7 +1176,7 @@
         <v>-43.175891999999997</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G10" t="s">
         <v>135</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B11">
         <v>-22.838093000000001</v>
@@ -1193,7 +1193,7 @@
         <v>-43.140821000000003</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G11" t="s">
         <v>135</v>
@@ -2040,7 +2040,7 @@
         <v>43</v>
       </c>
       <c r="E56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F56" t="s">
         <v>30</v>
@@ -2048,7 +2048,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B57">
         <v>-21.245633999999999</v>
@@ -2060,18 +2060,18 @@
         <v>23</v>
       </c>
       <c r="E57" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B58">
         <v>-25.246302</v>
@@ -2083,7 +2083,7 @@
         <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F58" t="s">
         <v>102</v>
@@ -2097,16 +2097,16 @@
         <v>77</v>
       </c>
       <c r="B59">
-        <v>-22.37</v>
+        <v>-22.451575999999999</v>
       </c>
       <c r="C59">
-        <v>-40.04</v>
+        <v>-40.044970999999997</v>
       </c>
       <c r="D59" t="s">
         <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F59" t="s">
         <v>30</v>
@@ -2114,25 +2114,25 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B60">
-        <v>5.2855800000000004</v>
+        <v>5.2861669999999998</v>
       </c>
       <c r="C60">
-        <v>-50.104092000000001</v>
+        <v>-50.104095000000001</v>
       </c>
       <c r="D60" t="s">
         <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F60" t="s">
+        <v>171</v>
+      </c>
+      <c r="G60" t="s">
         <v>172</v>
-      </c>
-      <c r="G60" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2643,50 +2643,50 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B89">
-        <v>37.594048000000001</v>
+        <v>1.246043</v>
       </c>
       <c r="C89">
-        <v>121.40307</v>
+        <v>103.60845</v>
       </c>
       <c r="D89" t="s">
         <v>27</v>
       </c>
       <c r="F89" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="G89" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="B90">
-        <v>-24.78</v>
+        <v>37.594048000000001</v>
       </c>
       <c r="C90">
-        <v>-42.5</v>
+        <v>121.40307</v>
       </c>
       <c r="D90" t="s">
         <v>27</v>
       </c>
       <c r="F90" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B91">
-        <v>-24.68</v>
+        <v>-24.78</v>
       </c>
       <c r="C91">
         <v>-42.5</v>
@@ -2703,13 +2703,13 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B92">
-        <v>-24.63</v>
+        <v>-24.68</v>
       </c>
       <c r="C92">
-        <v>-42.41</v>
+        <v>-42.5</v>
       </c>
       <c r="D92" t="s">
         <v>27</v>
@@ -2723,13 +2723,13 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B93">
-        <v>-24.67</v>
+        <v>-24.63</v>
       </c>
       <c r="C93">
-        <v>-42.38</v>
+        <v>-42.41</v>
       </c>
       <c r="D93" t="s">
         <v>27</v>
@@ -2743,13 +2743,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B94">
-        <v>-24.54</v>
+        <v>-24.67</v>
       </c>
       <c r="C94">
-        <v>-42.46</v>
+        <v>-42.38</v>
       </c>
       <c r="D94" t="s">
         <v>27</v>
@@ -2763,13 +2763,13 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="B95">
-        <v>-24.59</v>
+        <v>-24.54</v>
       </c>
       <c r="C95">
-        <v>-42.56</v>
+        <v>-42.46</v>
       </c>
       <c r="D95" t="s">
         <v>27</v>
@@ -2783,13 +2783,13 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="B96">
-        <v>-24.74</v>
+        <v>-24.59</v>
       </c>
       <c r="C96">
-        <v>-42.51</v>
+        <v>-42.56</v>
       </c>
       <c r="D96" t="s">
         <v>27</v>
@@ -2803,13 +2803,13 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="B97">
-        <v>-25.798373999999999</v>
+        <v>-24.74</v>
       </c>
       <c r="C97">
-        <v>-43.262680000000003</v>
+        <v>-42.51</v>
       </c>
       <c r="D97" t="s">
         <v>27</v>
@@ -2818,18 +2818,18 @@
         <v>102</v>
       </c>
       <c r="G97" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B98">
-        <v>-25.671883000000001</v>
+        <v>-25.798373999999999</v>
       </c>
       <c r="C98">
-        <v>-43.205939999999998</v>
+        <v>-43.262680000000003</v>
       </c>
       <c r="D98" t="s">
         <v>27</v>
@@ -2843,13 +2843,13 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B99">
-        <v>-25.226118</v>
+        <v>-25.671883000000001</v>
       </c>
       <c r="C99">
-        <v>-42.56982</v>
+        <v>-43.205939999999998</v>
       </c>
       <c r="D99" t="s">
         <v>27</v>
@@ -2858,18 +2858,18 @@
         <v>102</v>
       </c>
       <c r="G99" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="B100">
-        <v>-24.685623</v>
+        <v>-25.226118</v>
       </c>
       <c r="C100">
-        <v>-42.293922000000002</v>
+        <v>-42.56982</v>
       </c>
       <c r="D100" t="s">
         <v>27</v>
@@ -2878,69 +2878,72 @@
         <v>102</v>
       </c>
       <c r="G100" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B101">
-        <v>-22.1</v>
+        <v>-24.685623</v>
       </c>
       <c r="C101">
-        <v>-39.909999999999997</v>
+        <v>-42.293922000000002</v>
       </c>
       <c r="D101" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="F101" t="s">
-        <v>30</v>
+        <v>102</v>
+      </c>
+      <c r="G101" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B102">
-        <v>-23.08</v>
+        <v>-22.1</v>
       </c>
       <c r="C102">
-        <v>-40.99</v>
+        <v>-39.909999999999997</v>
       </c>
       <c r="D102" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F102" t="s">
         <v>30</v>
-      </c>
-      <c r="G102" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="B103">
+        <v>-23.08</v>
+      </c>
+      <c r="C103">
+        <v>-40.99</v>
       </c>
       <c r="D103" t="s">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="F103" t="s">
         <v>30</v>
+      </c>
+      <c r="G103" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B104">
-        <v>4.5487399999999996</v>
-      </c>
-      <c r="C104">
-        <v>4.5609250000000001</v>
+        <v>116</v>
       </c>
       <c r="D104" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="F104" t="s">
         <v>30</v>
@@ -2948,16 +2951,16 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B105">
-        <v>-22.14</v>
+        <v>4.5487399999999996</v>
       </c>
       <c r="C105">
-        <v>-39.92</v>
+        <v>4.5609250000000001</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="F105" t="s">
         <v>30</v>
@@ -2965,7 +2968,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B106">
         <v>-22.14</v>
@@ -2982,58 +2985,64 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B107">
-        <v>-23.3827</v>
+        <v>-22.14</v>
       </c>
       <c r="C107">
-        <v>-40.073999999999998</v>
+        <v>-39.92</v>
       </c>
       <c r="D107" t="s">
         <v>23</v>
       </c>
-      <c r="E107" t="s">
-        <v>122</v>
-      </c>
       <c r="F107" t="s">
-        <v>102</v>
-      </c>
-      <c r="G107" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B108">
-        <v>-22.657520000000002</v>
+        <v>-23.3827</v>
       </c>
       <c r="C108">
-        <v>-40.140785000000001</v>
+        <v>-40.073999999999998</v>
       </c>
       <c r="D108" t="s">
         <v>23</v>
       </c>
+      <c r="E108" t="s">
+        <v>122</v>
+      </c>
       <c r="F108" t="s">
-        <v>30</v>
+        <v>102</v>
+      </c>
+      <c r="G108" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B109">
+        <v>-22.657520000000002</v>
+      </c>
+      <c r="C109">
+        <v>-40.140785000000001</v>
+      </c>
+      <c r="D109" t="s">
+        <v>23</v>
+      </c>
+      <c r="F109" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="D109" t="s">
-        <v>48</v>
-      </c>
-      <c r="F109" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="D110" t="s">
         <v>48</v>
@@ -3042,58 +3051,49 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+    <row r="111" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D111" t="s">
+        <v>48</v>
+      </c>
+      <c r="F111" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>127</v>
       </c>
-      <c r="B111">
+      <c r="B112">
         <v>-21.33</v>
       </c>
-      <c r="C111">
+      <c r="C112">
         <v>-40.049999999999997</v>
       </c>
-      <c r="D111" t="s">
-        <v>27</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="D112" t="s">
+        <v>27</v>
+      </c>
+      <c r="E112" t="s">
         <v>128</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F112" t="s">
         <v>129</v>
       </c>
-      <c r="G111" t="s">
+      <c r="G112" t="s">
         <v>139</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B112">
-        <v>-22.436900000000001</v>
-      </c>
-      <c r="C112">
-        <v>-40.425800000000002</v>
-      </c>
-      <c r="D112" t="s">
-        <v>48</v>
-      </c>
-      <c r="F112" t="s">
-        <v>30</v>
-      </c>
-      <c r="G112" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B113">
-        <v>-22.374779</v>
+        <v>-22.436900000000001</v>
       </c>
       <c r="C113">
-        <v>-40.417454999999997</v>
+        <v>-40.425800000000002</v>
       </c>
       <c r="D113" t="s">
         <v>48</v>
@@ -3102,11 +3102,31 @@
         <v>30</v>
       </c>
       <c r="G113" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B114">
+        <v>-22.374779</v>
+      </c>
+      <c r="C114">
+        <v>-40.417454999999997</v>
+      </c>
+      <c r="D114" t="s">
+        <v>48</v>
+      </c>
+      <c r="F114" t="s">
+        <v>30</v>
+      </c>
+      <c r="G114" t="s">
         <v>151</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G113" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G114" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\projetos\ofi\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C9BC0C-60C9-436F-9E67-AACC10C0FCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0C0459-FA84-4CE4-86A3-8E8636F53FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
@@ -158,18 +158,9 @@
     <t>PBG</t>
   </si>
   <si>
-    <t xml:space="preserve">3R-2 (Ex-3+K6:L21ETROBRAS 61) </t>
-  </si>
-  <si>
-    <t>Semi-Sub/Prod/Perfuração</t>
-  </si>
-  <si>
     <t>ALPHA STAR (SS83)</t>
   </si>
   <si>
-    <t>Semi-Sub/Perfuração</t>
-  </si>
-  <si>
     <t>CONSTELATION</t>
   </si>
   <si>
@@ -272,9 +263,6 @@
     <t>ODN I (NS41)</t>
   </si>
   <si>
-    <t>Semi-Sub/Produção</t>
-  </si>
-  <si>
     <t>PAMPO 1 (PPM-1)</t>
   </si>
   <si>
@@ -579,6 +567,18 @@
   </si>
   <si>
     <t>PETROBRAS 82 (P-82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3R-2 (PETROBRAS 61) </t>
+  </si>
+  <si>
+    <t>Semi-Sub/Prod/Perfuracao</t>
+  </si>
+  <si>
+    <t>Semi-Sub/Perfuracao</t>
+  </si>
+  <si>
+    <t>Semi-Sub/Producao</t>
   </si>
 </sst>
 </file>
@@ -995,6 +995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G114"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1029,7 +1030,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1046,7 +1047,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1063,7 +1064,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1080,7 +1081,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1097,7 +1098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1114,7 +1115,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1131,7 +1132,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1148,9 +1149,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B9">
         <v>-22.848614000000001</v>
@@ -1159,15 +1160,15 @@
         <v>-43.146186999999998</v>
       </c>
       <c r="D9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B10">
         <v>-22.862100999999999</v>
@@ -1176,15 +1177,15 @@
         <v>-43.175891999999997</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B11">
         <v>-22.838093000000001</v>
@@ -1193,13 +1194,13 @@
         <v>-43.140821000000003</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1216,7 +1217,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1233,7 +1234,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1250,7 +1251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1270,7 +1271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -1290,7 +1291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>29</v>
       </c>
@@ -1310,7 +1311,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
@@ -1328,7 +1329,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1345,7 +1346,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1368,7 +1369,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>36</v>
       </c>
@@ -1391,7 +1392,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>38</v>
       </c>
@@ -1405,13 +1406,13 @@
         <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
@@ -1427,7 +1428,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="B24">
         <v>-23.516300000000001</v>
@@ -1436,7 +1437,7 @@
         <v>-41.061</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="E24" t="s">
         <v>34</v>
@@ -1450,7 +1451,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B25">
         <v>-19.86</v>
@@ -1459,10 +1460,10 @@
         <v>-39.619999999999997</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
         <v>30</v>
@@ -1470,7 +1471,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B26">
         <v>-22.87</v>
@@ -1479,7 +1480,7 @@
         <v>-43.13</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="F26" t="s">
         <v>30</v>
@@ -1487,7 +1488,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>-21.26</v>
@@ -1496,40 +1497,40 @@
         <v>-40.01</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="F27" t="s">
         <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>47</v>
-      </c>
-      <c r="D28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>50</v>
       </c>
       <c r="B30">
         <v>-21.251000000000001</v>
@@ -1544,12 +1545,12 @@
         <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B31">
         <v>-21.1599</v>
@@ -1561,26 +1562,26 @@
         <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B33">
         <v>-22.6</v>
@@ -1595,9 +1596,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B34">
         <v>-22.39</v>
@@ -1609,15 +1610,15 @@
         <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B35">
         <v>-22.46</v>
@@ -1629,15 +1630,15 @@
         <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F35" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B36">
         <v>-23.133800000000001</v>
@@ -1649,18 +1650,18 @@
         <v>27</v>
       </c>
       <c r="E36" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F36" t="s">
         <v>30</v>
       </c>
       <c r="G36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B37">
         <v>-22.95</v>
@@ -1672,18 +1673,18 @@
         <v>27</v>
       </c>
       <c r="E37" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F37" t="s">
         <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B38">
         <v>54.109959000000003</v>
@@ -1695,15 +1696,15 @@
         <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G38" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B39">
         <v>-25.139942000000001</v>
@@ -1715,18 +1716,18 @@
         <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F39" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G39" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B40">
         <v>-25.393484000000001</v>
@@ -1738,15 +1739,15 @@
         <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G40" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B41">
         <v>-25.202905999999999</v>
@@ -1758,15 +1759,15 @@
         <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G41" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B42">
         <v>-25.447762999999998</v>
@@ -1778,15 +1779,15 @@
         <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G42" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B43">
         <v>-25.490202</v>
@@ -1798,15 +1799,15 @@
         <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B44">
         <v>-25.517744</v>
@@ -1818,15 +1819,15 @@
         <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G44" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B45">
         <v>-22.0852</v>
@@ -1838,15 +1839,15 @@
         <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F45" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B46">
         <v>-21.882000000000001</v>
@@ -1858,18 +1859,18 @@
         <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F46" t="s">
         <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B47">
         <v>-22.22</v>
@@ -1884,12 +1885,12 @@
         <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B48">
         <v>-23.317</v>
@@ -1901,18 +1902,18 @@
         <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F48" t="s">
         <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B49">
         <v>-22.16</v>
@@ -1924,26 +1925,26 @@
         <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F49" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D50" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F50" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B51">
         <v>-21.33</v>
@@ -1955,26 +1956,26 @@
         <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G51" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="F52" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B53">
         <v>-21.975999999999999</v>
@@ -1994,7 +1995,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B54">
         <v>-23.5244</v>
@@ -2003,10 +2004,10 @@
         <v>-41.081299999999999</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="E54" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F54" t="s">
         <v>30</v>
@@ -2017,10 +2018,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D55" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="F55" t="s">
         <v>30</v>
@@ -2028,7 +2029,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B56">
         <v>-21.942143999999999</v>
@@ -2037,18 +2038,18 @@
         <v>-39.726315</v>
       </c>
       <c r="D56" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="E56" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F56" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B57">
         <v>-21.245633999999999</v>
@@ -2060,18 +2061,18 @@
         <v>23</v>
       </c>
       <c r="E57" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F57" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G57" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B58">
         <v>-25.246302</v>
@@ -2083,18 +2084,18 @@
         <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F58" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G58" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B59">
         <v>-22.451575999999999</v>
@@ -2106,15 +2107,15 @@
         <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F59" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B60">
         <v>5.2861669999999998</v>
@@ -2126,51 +2127,51 @@
         <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F60" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G60" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F61" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D63" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B64">
         <v>-23.39</v>
@@ -2179,29 +2180,29 @@
         <v>-41.4</v>
       </c>
       <c r="D64" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F64" t="s">
         <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F65" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B66">
         <v>-22.96</v>
@@ -2216,12 +2217,12 @@
         <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B67">
         <v>-22.672789000000002</v>
@@ -2230,18 +2231,18 @@
         <v>-40.546345000000002</v>
       </c>
       <c r="D67" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F67" t="s">
         <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B68">
         <v>-22.13</v>
@@ -2256,12 +2257,12 @@
         <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B69">
         <v>-22.561312000000001</v>
@@ -2270,7 +2271,7 @@
         <v>-40.122622999999997</v>
       </c>
       <c r="D69" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F69" t="s">
         <v>30</v>
@@ -2278,7 +2279,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B70" s="6">
         <v>-22.546870999999999</v>
@@ -2287,15 +2288,15 @@
         <v>-40.067348000000003</v>
       </c>
       <c r="D70" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F70" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B71">
         <v>-22.55</v>
@@ -2310,12 +2311,12 @@
         <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B72">
         <v>-22.34</v>
@@ -2330,12 +2331,12 @@
         <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B73">
         <v>-22.66</v>
@@ -2350,12 +2351,12 @@
         <v>30</v>
       </c>
       <c r="G73" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B74">
         <v>-22.633976000000001</v>
@@ -2364,7 +2365,7 @@
         <v>-40.093547999999998</v>
       </c>
       <c r="D74" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F74" t="s">
         <v>30</v>
@@ -2372,7 +2373,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B75">
         <v>-21.906445000000001</v>
@@ -2381,15 +2382,15 @@
         <v>-39.735923999999997</v>
       </c>
       <c r="D75" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F75" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B76">
         <v>-22.42</v>
@@ -2404,9 +2405,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B77">
         <v>-21.96</v>
@@ -2426,7 +2427,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B78">
         <v>-21.99</v>
@@ -2435,7 +2436,7 @@
         <v>-39.729999999999997</v>
       </c>
       <c r="D78" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F78" t="s">
         <v>30</v>
@@ -2443,7 +2444,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B79">
         <v>-22.62</v>
@@ -2452,18 +2453,18 @@
         <v>-39.979999999999997</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F79" t="s">
         <v>30</v>
       </c>
       <c r="G79" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B80">
         <v>-21.23</v>
@@ -2475,15 +2476,15 @@
         <v>27</v>
       </c>
       <c r="F80" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G80" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B81">
         <v>-22.701767</v>
@@ -2492,18 +2493,18 @@
         <v>-40.677059</v>
       </c>
       <c r="D81" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F81" t="s">
         <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B82">
         <v>-25.601856000000002</v>
@@ -2515,15 +2516,15 @@
         <v>27</v>
       </c>
       <c r="F82" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G82" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B83">
         <v>-25.328738999999999</v>
@@ -2535,15 +2536,15 @@
         <v>27</v>
       </c>
       <c r="F83" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G83" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B84">
         <v>-25.022000999999999</v>
@@ -2555,15 +2556,15 @@
         <v>27</v>
       </c>
       <c r="F84" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G84" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B85">
         <v>-25.656942000000001</v>
@@ -2575,15 +2576,15 @@
         <v>27</v>
       </c>
       <c r="F85" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G85" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B86">
         <v>-24.951167999999999</v>
@@ -2595,15 +2596,15 @@
         <v>27</v>
       </c>
       <c r="F86" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G86" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B87">
         <v>-24.776168999999999</v>
@@ -2615,15 +2616,15 @@
         <v>27</v>
       </c>
       <c r="F87" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G87" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B88">
         <v>-24.64</v>
@@ -2635,15 +2636,15 @@
         <v>27</v>
       </c>
       <c r="F88" t="s">
+        <v>98</v>
+      </c>
+      <c r="G88" t="s">
         <v>102</v>
       </c>
-      <c r="G88" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B89">
         <v>1.246043</v>
@@ -2661,9 +2662,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B90">
         <v>37.594048000000001</v>
@@ -2681,9 +2682,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B91">
         <v>-24.78</v>
@@ -2695,15 +2696,15 @@
         <v>27</v>
       </c>
       <c r="F91" t="s">
+        <v>98</v>
+      </c>
+      <c r="G91" t="s">
         <v>102</v>
       </c>
-      <c r="G91" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B92">
         <v>-24.68</v>
@@ -2715,15 +2716,15 @@
         <v>27</v>
       </c>
       <c r="F92" t="s">
+        <v>98</v>
+      </c>
+      <c r="G92" t="s">
         <v>102</v>
       </c>
-      <c r="G92" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B93">
         <v>-24.63</v>
@@ -2735,15 +2736,15 @@
         <v>27</v>
       </c>
       <c r="F93" t="s">
+        <v>98</v>
+      </c>
+      <c r="G93" t="s">
         <v>102</v>
       </c>
-      <c r="G93" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B94">
         <v>-24.67</v>
@@ -2755,15 +2756,15 @@
         <v>27</v>
       </c>
       <c r="F94" t="s">
+        <v>98</v>
+      </c>
+      <c r="G94" t="s">
         <v>102</v>
       </c>
-      <c r="G94" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B95">
         <v>-24.54</v>
@@ -2775,15 +2776,15 @@
         <v>27</v>
       </c>
       <c r="F95" t="s">
+        <v>98</v>
+      </c>
+      <c r="G95" t="s">
         <v>102</v>
       </c>
-      <c r="G95" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B96">
         <v>-24.59</v>
@@ -2795,15 +2796,15 @@
         <v>27</v>
       </c>
       <c r="F96" t="s">
+        <v>98</v>
+      </c>
+      <c r="G96" t="s">
         <v>102</v>
       </c>
-      <c r="G96" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B97">
         <v>-24.74</v>
@@ -2815,15 +2816,15 @@
         <v>27</v>
       </c>
       <c r="F97" t="s">
+        <v>98</v>
+      </c>
+      <c r="G97" t="s">
         <v>102</v>
       </c>
-      <c r="G97" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B98">
         <v>-25.798373999999999</v>
@@ -2835,15 +2836,15 @@
         <v>27</v>
       </c>
       <c r="F98" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G98" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B99">
         <v>-25.671883000000001</v>
@@ -2855,15 +2856,15 @@
         <v>27</v>
       </c>
       <c r="F99" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G99" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B100">
         <v>-25.226118</v>
@@ -2875,15 +2876,15 @@
         <v>27</v>
       </c>
       <c r="F100" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G100" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B101">
         <v>-24.685623</v>
@@ -2895,15 +2896,15 @@
         <v>27</v>
       </c>
       <c r="F101" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G101" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B102">
         <v>-22.1</v>
@@ -2912,15 +2913,15 @@
         <v>-39.909999999999997</v>
       </c>
       <c r="D102" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F102" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B103">
         <v>-23.08</v>
@@ -2929,21 +2930,21 @@
         <v>-40.99</v>
       </c>
       <c r="D103" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F103" t="s">
         <v>30</v>
       </c>
       <c r="G103" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D104" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F104" t="s">
         <v>30</v>
@@ -2951,7 +2952,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B105">
         <v>4.5487399999999996</v>
@@ -2960,15 +2961,15 @@
         <v>4.5609250000000001</v>
       </c>
       <c r="D105" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="F105" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B106">
         <v>-22.14</v>
@@ -2983,9 +2984,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B107">
         <v>-22.14</v>
@@ -3000,9 +3001,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B108">
         <v>-23.3827</v>
@@ -3014,18 +3015,18 @@
         <v>23</v>
       </c>
       <c r="E108" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F108" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G108" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B109">
         <v>-22.657520000000002</v>
@@ -3040,31 +3041,31 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D110" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F110" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="28.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D111" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F111" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B112">
         <v>-21.33</v>
@@ -3076,18 +3077,18 @@
         <v>27</v>
       </c>
       <c r="E112" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F112" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G112" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B113">
         <v>-22.436900000000001</v>
@@ -3096,18 +3097,18 @@
         <v>-40.425800000000002</v>
       </c>
       <c r="D113" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F113" t="s">
         <v>30</v>
       </c>
       <c r="G113" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B114">
         <v>-22.374779</v>
@@ -3116,17 +3117,26 @@
         <v>-40.417454999999997</v>
       </c>
       <c r="D114" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F114" t="s">
         <v>30</v>
       </c>
       <c r="G114" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G114" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G114" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Semi-Sub/Perfuracao"/>
+        <filter val="Semi-Sub/Perfuração"/>
+        <filter val="Semi-Sub/Prod/Perfuracao"/>
+        <filter val="Semi-Sub/Produção"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>